--- a/ExpenseTracker/ExpenseTracker.xlsx
+++ b/ExpenseTracker/ExpenseTracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arulmozhikumark/Desktop/Genspark-Training/ExpenseTracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B000EF-7743-5F44-A9FA-DF235A6F6C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEEEACD-94E1-E14A-824E-DF9A995DF980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="94">
   <si>
     <t>Endpoint</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>204 No Content, 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>≠≠≠</t>
   </si>
 </sst>
 </file>
@@ -666,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
@@ -1257,6 +1260,11 @@
         <v>92</v>
       </c>
     </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
